--- a/data/trans_orig/Q5412-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2007</t>
+          <t>Población según si es capaz de arreglarse en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>29448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66265</t>
+          <t>66462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84197</t>
+          <t>83778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94963</t>
+          <t>94662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148496</t>
+          <t>149111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160776</t>
+          <t>160774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129275</t>
+          <t>129502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51060</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68850</t>
+          <t>69460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123524</t>
+          <t>123328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30968</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40104</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55167</t>
+          <t>55562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>66272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6720</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5844</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5676</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64465</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111830</t>
+          <t>112943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99581</t>
+          <t>99565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107610</t>
+          <t>107441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116068</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>210565</t>
+          <t>211008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>221035</t>
+          <t>220962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102022</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110026</t>
+          <t>110010</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135552</t>
+          <t>135644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>149575</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>241619</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>257700</t>
+          <t>257861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>57103</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>478553</t>
+          <t>478759</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>493346</t>
+          <t>492669</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>636756</t>
+          <t>637559</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>658406</t>
+          <t>658506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1122757</t>
+          <t>1122205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1147422</t>
+          <t>1146969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2012</t>
+          <t>Población según si es capaz de arreglarse en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45686</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76855</t>
+          <t>78208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88970</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64174</t>
+          <t>63190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76110</t>
+          <t>76122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77733</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93319</t>
+          <t>93391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147684</t>
+          <t>147150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166989</t>
+          <t>167277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>23663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45496</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53879</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63680</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74932</t>
+          <t>75599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113244</t>
+          <t>112047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127305</t>
+          <t>126461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54100</t>
+          <t>53892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62871</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70625</t>
+          <t>69836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82182</t>
+          <t>81382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128087</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142818</t>
+          <t>142226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41637</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>68103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>79293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68001</t>
+          <t>68036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106134</t>
+          <t>107236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118650</t>
+          <t>118701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14255</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>32838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96370</t>
+          <t>95435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109270</t>
+          <t>109323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118584</t>
+          <t>118661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134063</t>
+          <t>133968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220292</t>
+          <t>221388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239971</t>
+          <t>240223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112048</t>
+          <t>111651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119730</t>
+          <t>119724</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140583</t>
+          <t>140467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156274</t>
+          <t>156529</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257391</t>
+          <t>256067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274644</t>
+          <t>274249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97162</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93666</t>
+          <t>93682</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137205</t>
+          <t>137367</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>509899</t>
+          <t>511721</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>535715</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>645813</t>
+          <t>646022</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>680031</t>
+          <t>679899</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1165407</t>
+          <t>1165245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1208946</t>
+          <t>1208930</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2016</t>
+          <t>Población según si es capaz de arreglarse en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>48090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73451</t>
+          <t>73143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85400</t>
+          <t>85166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>20440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79201</t>
+          <t>79359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86433</t>
+          <t>86428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>99586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112529</t>
+          <t>112542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183536</t>
+          <t>182083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197000</t>
+          <t>197434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56649</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127507</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140964</t>
+          <t>141354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57732</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63947</t>
+          <t>63935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78735</t>
+          <t>78324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90305</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140909</t>
+          <t>138939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153320</t>
+          <t>153374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48271</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79989</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90281</t>
+          <t>90319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>46800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49151</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62770</t>
+          <t>62368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91966</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107855</t>
+          <t>107914</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101910</t>
+          <t>102022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>129869</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143824</t>
+          <t>142743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237050</t>
+          <t>235595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252404</t>
+          <t>251568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124734</t>
+          <t>125665</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133344</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164107</t>
+          <t>162158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174974</t>
+          <t>174957</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>294649</t>
+          <t>293941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>306989</t>
+          <t>306905</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>39457</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71489</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>94845</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>558757</t>
+          <t>558731</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>576634</t>
+          <t>577048</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>706442</t>
+          <t>705530</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>739757</t>
+          <t>738474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1275823</t>
+          <t>1274414</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1312162</t>
+          <t>1310045</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2023</t>
+          <t>Población según si es capaz de arreglarse en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53789</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107472</t>
+          <t>107775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116135</t>
+          <t>116374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37242</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69205</t>
+          <t>68998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78166</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99272</t>
+          <t>98031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113357</t>
+          <t>112597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172458</t>
+          <t>171272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188640</t>
+          <t>188115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58966</t>
+          <t>58635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67925</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71555</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80575</t>
+          <t>80475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133806</t>
+          <t>134006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70712</t>
+          <t>70665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>89532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>96815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161849</t>
+          <t>162161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170627</t>
+          <t>170440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34211</t>
+          <t>34305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81528</t>
+          <t>81233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88416</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11219</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52332</t>
+          <t>52218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>57677</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>50981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58076</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105543</t>
+          <t>105323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114300</t>
+          <t>114038</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28129</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114936</t>
+          <t>115159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121830</t>
+          <t>121865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311041</t>
+          <t>311464</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>337863</t>
+          <t>337011</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>434307</t>
+          <t>435049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>458283</t>
+          <t>458359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>140016</t>
+          <t>140161</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145842</t>
+          <t>145830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174883</t>
+          <t>175150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>182766</t>
+          <t>182895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318210</t>
+          <t>317800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327220</t>
+          <t>327526</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106782</t>
+          <t>106382</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77602</t>
+          <t>74508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>136556</t>
+          <t>135928</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>609516</t>
+          <t>609202</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>627322</t>
+          <t>626459</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>926656</t>
+          <t>927056</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>991637</t>
+          <t>992558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1547061</t>
+          <t>1547689</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1606015</t>
+          <t>1609109</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5412-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>29714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66462</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73806</t>
+          <t>73810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60638</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83778</t>
+          <t>83409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94662</t>
+          <t>94756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149111</t>
+          <t>148832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>160774</t>
+          <t>160632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129502</t>
+          <t>130558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69460</t>
+          <t>68875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123328</t>
+          <t>122650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55562</t>
+          <t>55425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>64304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112943</t>
+          <t>111768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107441</t>
+          <t>107421</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>115981</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>211008</t>
+          <t>211357</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>220962</t>
+          <t>221123</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102025</t>
+          <t>101190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110010</t>
+          <t>110003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135644</t>
+          <t>135869</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149575</t>
+          <t>149641</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>257861</t>
+          <t>257806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57103</t>
+          <t>57075</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>478759</t>
+          <t>477618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>492669</t>
+          <t>492565</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>637559</t>
+          <t>636668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>658506</t>
+          <t>658288</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1122205</t>
+          <t>1122233</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1146969</t>
+          <t>1148214</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37055</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>45692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78208</t>
+          <t>77341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>89012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63190</t>
+          <t>63843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>76139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77287</t>
+          <t>77150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93391</t>
+          <t>93201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147150</t>
+          <t>147827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167277</t>
+          <t>167031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>53807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63371</t>
+          <t>62844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75599</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>111838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126461</t>
+          <t>126453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>53675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>62878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69836</t>
+          <t>69723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81382</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>127748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142226</t>
+          <t>142626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48888</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68103</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79293</t>
+          <t>79351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>57465</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68036</t>
+          <t>68019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107236</t>
+          <t>106819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118701</t>
+          <t>117811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32838</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95435</t>
+          <t>96848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109323</t>
+          <t>109194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118661</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133968</t>
+          <t>134032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221388</t>
+          <t>220530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240223</t>
+          <t>241017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>28640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111651</t>
+          <t>110900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119710</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140467</t>
+          <t>140365</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156529</t>
+          <t>156243</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256067</t>
+          <t>256529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274249</t>
+          <t>273823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>60690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93682</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>135784</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>511721</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>535715</t>
+          <t>535644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>646022</t>
+          <t>646951</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>679899</t>
+          <t>682285</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1165245</t>
+          <t>1166828</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1208930</t>
+          <t>1208349</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48090</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>72544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85166</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79359</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86428</t>
+          <t>86436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99586</t>
+          <t>99300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112542</t>
+          <t>112513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182083</t>
+          <t>182837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197434</t>
+          <t>197429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>57111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129224</t>
+          <t>129454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141354</t>
+          <t>141018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57737</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63935</t>
+          <t>63949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78324</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>90292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138939</t>
+          <t>140937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153374</t>
+          <t>153558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38165</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>48304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79593</t>
+          <t>79903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90319</t>
+          <t>90311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39742</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46800</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>49352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62368</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92577</t>
+          <t>92118</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107914</t>
+          <t>107364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102022</t>
+          <t>101941</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110405</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129869</t>
+          <t>130224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142743</t>
+          <t>143179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235595</t>
+          <t>235729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251568</t>
+          <t>251751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125665</t>
+          <t>125348</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134168</t>
+          <t>133364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162158</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174957</t>
+          <t>174972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>293941</t>
+          <t>293971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>306905</t>
+          <t>307041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39457</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>72647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>95326</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>558731</t>
+          <t>560391</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>577048</t>
+          <t>577316</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>705530</t>
+          <t>705284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>738474</t>
+          <t>739064</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1274414</t>
+          <t>1273933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1310045</t>
+          <t>1310910</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55009</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51273</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57890</t>
+          <t>59778</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60846</t>
+          <t>62653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>112899</t>
+          <t>119848</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>115217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116374</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>31700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28261</t>
+          <t>30251</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74563</t>
+          <t>81759</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>76029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78112</t>
+          <t>85522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>106877</t>
+          <t>111691</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98031</t>
+          <t>103628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112597</t>
+          <t>117844</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>181439</t>
+          <t>193450</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171272</t>
+          <t>183768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188115</t>
+          <t>201443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,17 +11383,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -11496,17 +11496,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64094</t>
+          <t>63039</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58635</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>66954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>74946</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70993</t>
+          <t>69922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>78699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>137985</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134006</t>
+          <t>131496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145896</t>
+          <t>143666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -11839,27 +11839,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73363</t>
+          <t>81896</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70665</t>
+          <t>79026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>93655</t>
+          <t>100079</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89532</t>
+          <t>95726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96815</t>
+          <t>103833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>167017</t>
+          <t>181975</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162161</t>
+          <t>177306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170440</t>
+          <t>185736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32753</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>35983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52669</t>
+          <t>54617</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49257</t>
+          <t>50916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55111</t>
+          <t>57444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>85423</t>
+          <t>89025</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81233</t>
+          <t>84615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>92062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55440</t>
+          <t>55374</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52218</t>
+          <t>52408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57677</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>54878</t>
+          <t>56742</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>60016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>110318</t>
+          <t>112115</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105323</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114038</t>
+          <t>116099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>119591</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115159</t>
+          <t>140809</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121865</t>
+          <t>149546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>329513</t>
+          <t>153089</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311464</t>
+          <t>147308</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>337011</t>
+          <t>158398</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>449104</t>
+          <t>299761</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>435049</t>
+          <t>291177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>458359</t>
+          <t>305873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,17 +13133,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>143861</t>
+          <t>159540</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>140161</t>
+          <t>154873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>162208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,17 +13246,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>179607</t>
+          <t>204740</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>198864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>208246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>323468</t>
+          <t>364280</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317800</t>
+          <t>358676</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327526</t>
+          <t>368956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40976</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>100912</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>113286</t>
+          <t>120918</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>135928</t>
+          <t>138105</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>618673</t>
+          <t>682757</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>609202</t>
+          <t>672365</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>626459</t>
+          <t>691451</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>951657</t>
+          <t>815683</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>927056</t>
+          <t>802054</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>992558</t>
+          <t>827597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1570331</t>
+          <t>1498439</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1547689</t>
+          <t>1481252</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1609109</t>
+          <t>1513298</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
